--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486555_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486555_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.5069</v>
+        <v>7.5002</v>
       </c>
       <c r="E2" t="n">
-        <v>6.1346</v>
+        <v>7.0972</v>
       </c>
       <c r="F2" t="n">
-        <v>0.3722</v>
+        <v>0.403</v>
       </c>
       <c r="G2" t="n">
         <v>5.9436</v>
@@ -610,13 +610,13 @@
         <v>1.7401</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.8495</v>
+        <v>0.1439</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.6165</v>
+        <v>0.3461</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.233</v>
+        <v>-0.2022</v>
       </c>
       <c r="V2" t="n">
         <v>0.7602</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.554</v>
+        <v>5.0753</v>
       </c>
       <c r="E3" t="n">
-        <v>3.079</v>
+        <v>2.477</v>
       </c>
       <c r="F3" t="n">
-        <v>2.475</v>
+        <v>2.5983</v>
       </c>
       <c r="G3" t="n">
         <v>2.0806</v>
@@ -688,13 +688,13 @@
         <v>2.8276</v>
       </c>
       <c r="S3" t="n">
-        <v>0.8633</v>
+        <v>0.3845</v>
       </c>
       <c r="T3" t="n">
-        <v>1.0707</v>
+        <v>0.4687</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.2074</v>
+        <v>-0.08409999999999999</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.6134</v>
+        <v>4.6579</v>
       </c>
       <c r="E4" t="n">
-        <v>4.6848</v>
+        <v>4.8218</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.07140000000000001</v>
+        <v>-0.1639</v>
       </c>
       <c r="G4" t="n">
         <v>4.815</v>
@@ -766,13 +766,13 @@
         <v>1.9576</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.2467</v>
+        <v>-0.2022</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0601</v>
+        <v>0.1971</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.3068</v>
+        <v>-0.3993</v>
       </c>
       <c r="V4" t="n">
         <v>-1.695</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>F. SCHOTT</t>
+          <t>J. CONE</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>4.0615</v>
+        <v>3.5206</v>
       </c>
       <c r="E5" t="n">
-        <v>1.8535</v>
+        <v>0.2789</v>
       </c>
       <c r="F5" t="n">
-        <v>2.2079</v>
+        <v>3.2417</v>
       </c>
       <c r="G5" t="n">
-        <v>0.8193</v>
+        <v>4.5829</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.435</v>
+        <v>2.0528</v>
       </c>
       <c r="I5" t="n">
-        <v>1.2543</v>
+        <v>2.5301</v>
       </c>
       <c r="J5" t="n">
-        <v>0.7246</v>
+        <v>3.5932</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.6141</v>
+        <v>0.8942</v>
       </c>
       <c r="L5" t="n">
-        <v>1.3387</v>
+        <v>2.699</v>
       </c>
       <c r="M5" t="n">
-        <v>0.09470000000000001</v>
+        <v>0.9897</v>
       </c>
       <c r="N5" t="n">
-        <v>0.1792</v>
+        <v>1.1586</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.08450000000000001</v>
+        <v>-0.1689</v>
       </c>
       <c r="P5" t="n">
-        <v>0.435</v>
+        <v>-1.0875</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.0875</v>
+        <v>-3.2626</v>
       </c>
       <c r="R5" t="n">
-        <v>1.5225</v>
+        <v>2.1751</v>
       </c>
       <c r="S5" t="n">
-        <v>2.8072</v>
+        <v>0.2205</v>
       </c>
       <c r="T5" t="n">
-        <v>2.0213</v>
+        <v>-0.0517</v>
       </c>
       <c r="U5" t="n">
-        <v>0.7859</v>
+        <v>0.2722</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>-0.1952</v>
       </c>
       <c r="W5" t="n">
-        <v>0.1952</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
         <v>-0.1952</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. CONE</t>
+          <t>F. SCHOTT</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,64 +877,64 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>3.379</v>
+        <v>2.7294</v>
       </c>
       <c r="E6" t="n">
-        <v>0.3222</v>
+        <v>0.8297</v>
       </c>
       <c r="F6" t="n">
-        <v>3.0567</v>
+        <v>1.8997</v>
       </c>
       <c r="G6" t="n">
-        <v>4.5829</v>
+        <v>0.8193</v>
       </c>
       <c r="H6" t="n">
-        <v>2.0528</v>
+        <v>-0.435</v>
       </c>
       <c r="I6" t="n">
-        <v>2.5301</v>
+        <v>1.2543</v>
       </c>
       <c r="J6" t="n">
-        <v>3.5932</v>
+        <v>0.7246</v>
       </c>
       <c r="K6" t="n">
-        <v>0.8942</v>
+        <v>-0.6141</v>
       </c>
       <c r="L6" t="n">
-        <v>2.699</v>
+        <v>1.3387</v>
       </c>
       <c r="M6" t="n">
-        <v>0.9897</v>
+        <v>0.09470000000000001</v>
       </c>
       <c r="N6" t="n">
-        <v>1.1586</v>
+        <v>0.1792</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.1689</v>
+        <v>-0.08450000000000001</v>
       </c>
       <c r="P6" t="n">
+        <v>0.435</v>
+      </c>
+      <c r="Q6" t="n">
         <v>-1.0875</v>
       </c>
-      <c r="Q6" t="n">
-        <v>-3.2626</v>
-      </c>
       <c r="R6" t="n">
-        <v>2.1751</v>
+        <v>1.5225</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0788</v>
+        <v>1.4751</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.008399999999999999</v>
+        <v>0.9974</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0872</v>
+        <v>0.4777</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.1952</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>0.1952</v>
       </c>
       <c r="X6" t="n">
         <v>-0.1952</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>3.0606</v>
+        <v>2.4595</v>
       </c>
       <c r="E7" t="n">
-        <v>3.2517</v>
+        <v>2.8047</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.1911</v>
+        <v>-0.3452</v>
       </c>
       <c r="G7" t="n">
         <v>2.1183</v>
@@ -1000,13 +1000,13 @@
         <v>1.7401</v>
       </c>
       <c r="S7" t="n">
-        <v>0.3323</v>
+        <v>-0.2689</v>
       </c>
       <c r="T7" t="n">
-        <v>0.1971</v>
+        <v>-0.2499</v>
       </c>
       <c r="U7" t="n">
-        <v>0.1352</v>
+        <v>-0.0189</v>
       </c>
       <c r="V7" t="n">
         <v>-1.13</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>N. GALETTE</t>
+          <t>T. ROTEGARD</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.6748</v>
+        <v>1.6841</v>
       </c>
       <c r="E8" t="n">
-        <v>1.6596</v>
+        <v>2.6241</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0152</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="G8" t="n">
-        <v>0.6956</v>
+        <v>2.7345</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.1037</v>
+        <v>0.4196</v>
       </c>
       <c r="I8" t="n">
-        <v>1.7993</v>
+        <v>2.3149</v>
       </c>
       <c r="J8" t="n">
-        <v>0.5204</v>
+        <v>2.4078</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.6813</v>
+        <v>0.073</v>
       </c>
       <c r="L8" t="n">
-        <v>2.2018</v>
+        <v>2.3348</v>
       </c>
       <c r="M8" t="n">
-        <v>0.1752</v>
+        <v>0.3267</v>
       </c>
       <c r="N8" t="n">
-        <v>0.5776</v>
+        <v>0.3466</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.4024</v>
+        <v>-0.0199</v>
       </c>
       <c r="P8" t="n">
-        <v>2.3926</v>
+        <v>1.0875</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>2.3926</v>
+        <v>1.0875</v>
       </c>
       <c r="S8" t="n">
-        <v>1.9766</v>
+        <v>0.3172</v>
       </c>
       <c r="T8" t="n">
-        <v>1.1392</v>
+        <v>0.2163</v>
       </c>
       <c r="U8" t="n">
-        <v>0.8373</v>
+        <v>0.1009</v>
       </c>
       <c r="V8" t="n">
-        <v>-3.3899</v>
+        <v>-2.4552</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-3.3899</v>
+        <v>-2.4552</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>T. ROTEGARD</t>
+          <t>N. GALETTE</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.865</v>
+        <v>1.0111</v>
       </c>
       <c r="E9" t="n">
-        <v>1.9283</v>
+        <v>1.0576</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.0633</v>
+        <v>-0.0464</v>
       </c>
       <c r="G9" t="n">
-        <v>2.7345</v>
+        <v>0.6956</v>
       </c>
       <c r="H9" t="n">
-        <v>0.4196</v>
+        <v>-1.1037</v>
       </c>
       <c r="I9" t="n">
-        <v>2.3149</v>
+        <v>1.7993</v>
       </c>
       <c r="J9" t="n">
-        <v>2.4078</v>
+        <v>0.5204</v>
       </c>
       <c r="K9" t="n">
-        <v>0.073</v>
+        <v>-1.6813</v>
       </c>
       <c r="L9" t="n">
-        <v>2.3348</v>
+        <v>2.2018</v>
       </c>
       <c r="M9" t="n">
-        <v>0.3267</v>
+        <v>0.1752</v>
       </c>
       <c r="N9" t="n">
-        <v>0.3466</v>
+        <v>0.5776</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.0199</v>
+        <v>-0.4024</v>
       </c>
       <c r="P9" t="n">
-        <v>1.0875</v>
+        <v>2.3926</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.0875</v>
+        <v>2.3926</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.5018</v>
+        <v>1.3129</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.4795</v>
+        <v>0.5372</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.0224</v>
+        <v>0.7756999999999999</v>
       </c>
       <c r="V9" t="n">
-        <v>-2.4552</v>
+        <v>-3.3899</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-2.4552</v>
+        <v>-3.3899</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>E. WEMBI</t>
+          <t>S. LITTLESON</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,40 +1189,40 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.0742</v>
+        <v>0.8676</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.4415</v>
+        <v>-0.706</v>
       </c>
       <c r="F10" t="n">
-        <v>0.5157</v>
+        <v>1.5736</v>
       </c>
       <c r="G10" t="n">
-        <v>2.1272</v>
+        <v>0.3507</v>
       </c>
       <c r="H10" t="n">
-        <v>0.0274</v>
+        <v>0.3531</v>
       </c>
       <c r="I10" t="n">
-        <v>2.0997</v>
+        <v>-0.0024</v>
       </c>
       <c r="J10" t="n">
-        <v>1.1375</v>
+        <v>-0.156</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.8331</v>
+        <v>-0.4071</v>
       </c>
       <c r="L10" t="n">
-        <v>1.9706</v>
+        <v>0.251</v>
       </c>
       <c r="M10" t="n">
-        <v>0.9897</v>
+        <v>0.5067</v>
       </c>
       <c r="N10" t="n">
-        <v>0.8606</v>
+        <v>0.7601</v>
       </c>
       <c r="O10" t="n">
-        <v>0.1291</v>
+        <v>-0.2534</v>
       </c>
       <c r="P10" t="n">
         <v>-0.2175</v>
@@ -1234,28 +1234,28 @@
         <v>1.0875</v>
       </c>
       <c r="S10" t="n">
-        <v>0.0547</v>
+        <v>-0.2004</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.274</v>
+        <v>-0.3749</v>
       </c>
       <c r="U10" t="n">
-        <v>0.3287</v>
+        <v>0.1745</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.8902</v>
+        <v>0.9347</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.8902</v>
+        <v>-0.1952</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>S. LITTLESON</t>
+          <t>E. WEMBI</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,40 +1267,40 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>0.0678</v>
+        <v>0.3671</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.29</v>
+        <v>0.0055</v>
       </c>
       <c r="F11" t="n">
-        <v>1.3578</v>
+        <v>0.3615</v>
       </c>
       <c r="G11" t="n">
-        <v>0.3507</v>
+        <v>2.1272</v>
       </c>
       <c r="H11" t="n">
-        <v>0.3531</v>
+        <v>0.0274</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.0024</v>
+        <v>2.0997</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.156</v>
+        <v>1.1375</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.4071</v>
+        <v>-0.8331</v>
       </c>
       <c r="L11" t="n">
-        <v>0.251</v>
+        <v>1.9706</v>
       </c>
       <c r="M11" t="n">
-        <v>0.5067</v>
+        <v>0.9897</v>
       </c>
       <c r="N11" t="n">
-        <v>0.7601</v>
+        <v>0.8606</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.2534</v>
+        <v>0.1291</v>
       </c>
       <c r="P11" t="n">
         <v>-0.2175</v>
@@ -1312,22 +1312,22 @@
         <v>1.0875</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.0002</v>
+        <v>0.3476</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.9589</v>
+        <v>0.173</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.0412</v>
+        <v>0.1745</v>
       </c>
       <c r="V11" t="n">
-        <v>0.9347</v>
+        <v>-1.8902</v>
       </c>
       <c r="W11" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.1952</v>
+        <v>-1.8902</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.0483</v>
+        <v>-0.3381</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.3284</v>
+        <v>-0.3716</v>
       </c>
       <c r="F12" t="n">
-        <v>0.2801</v>
+        <v>0.0335</v>
       </c>
       <c r="G12" t="n">
         <v>0.6296</v>
@@ -1390,13 +1390,13 @@
         <v>1.0875</v>
       </c>
       <c r="S12" t="n">
-        <v>0.6696</v>
+        <v>0.3797</v>
       </c>
       <c r="T12" t="n">
-        <v>0.0601</v>
+        <v>0.0168</v>
       </c>
       <c r="U12" t="n">
-        <v>0.6095</v>
+        <v>0.3629</v>
       </c>
       <c r="V12" t="n">
         <v>-1.13</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-1.9621</v>
+        <v>-0.6605</v>
       </c>
       <c r="E13" t="n">
-        <v>-4.4809</v>
+        <v>-3.5183</v>
       </c>
       <c r="F13" t="n">
-        <v>2.5188</v>
+        <v>2.8579</v>
       </c>
       <c r="G13" t="n">
         <v>-0.5406</v>
@@ -1468,13 +1468,13 @@
         <v>3.0451</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.204</v>
+        <v>0.09760000000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.6850000000000001</v>
+        <v>0.2776</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.519</v>
+        <v>-0.18</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -1501,19 +1501,19 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>27.8468</v>
+        <v>28.8742</v>
       </c>
       <c r="E14" t="n">
-        <v>16.3729</v>
+        <v>17.4006</v>
       </c>
       <c r="F14" t="n">
-        <v>11.4736</v>
+        <v>11.4737</v>
       </c>
       <c r="G14" t="n">
         <v>26.3567</v>
       </c>
       <c r="H14" t="n">
-        <v>8.622400000000001</v>
+        <v>8.622399999999999</v>
       </c>
       <c r="I14" t="n">
         <v>17.7342</v>
@@ -1522,13 +1522,13 @@
         <v>25.6165</v>
       </c>
       <c r="K14" t="n">
-        <v>3.013400000000001</v>
+        <v>3.0134</v>
       </c>
       <c r="L14" t="n">
         <v>22.60300000000001</v>
       </c>
       <c r="M14" t="n">
-        <v>0.7401000000000002</v>
+        <v>0.7401000000000001</v>
       </c>
       <c r="N14" t="n">
         <v>5.609</v>
@@ -1546,13 +1546,13 @@
         <v>21.7507</v>
       </c>
       <c r="S14" t="n">
-        <v>2.980300000000001</v>
+        <v>4.0075</v>
       </c>
       <c r="T14" t="n">
-        <v>1.526199999999999</v>
+        <v>2.5537</v>
       </c>
       <c r="U14" t="n">
-        <v>1.454</v>
+        <v>1.4539</v>
       </c>
       <c r="V14" t="n">
         <v>-10.1906</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>N. MC MULLEN</t>
+          <t>M. CAICEDO SANCHEZ</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.5707</v>
+        <v>0.7621</v>
       </c>
       <c r="E15" t="n">
-        <v>0.8767</v>
+        <v>1.6373</v>
       </c>
       <c r="F15" t="n">
-        <v>0.694</v>
+        <v>-0.8752</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.5832000000000001</v>
+        <v>1.4499</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.666</v>
+        <v>0.7208</v>
       </c>
       <c r="I15" t="n">
-        <v>0.0829</v>
+        <v>0.7291</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.7584</v>
+        <v>2.3115</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.7966</v>
+        <v>0.6086</v>
       </c>
       <c r="L15" t="n">
-        <v>0.0382</v>
+        <v>1.7029</v>
       </c>
       <c r="M15" t="n">
-        <v>0.1752</v>
+        <v>-0.8616</v>
       </c>
       <c r="N15" t="n">
-        <v>0.1306</v>
+        <v>0.1122</v>
       </c>
       <c r="O15" t="n">
-        <v>0.0446</v>
+        <v>-0.9738</v>
       </c>
       <c r="P15" t="n">
-        <v>-2.6101</v>
+        <v>0.435</v>
       </c>
       <c r="Q15" t="n">
-        <v>-3.2626</v>
+        <v>-1.0875</v>
       </c>
       <c r="R15" t="n">
-        <v>0.6525</v>
+        <v>1.5225</v>
       </c>
       <c r="S15" t="n">
-        <v>2.504</v>
+        <v>0.0072</v>
       </c>
       <c r="T15" t="n">
-        <v>2.6377</v>
+        <v>0.4134</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.1338</v>
+        <v>-0.4062</v>
       </c>
       <c r="V15" t="n">
-        <v>2.2599</v>
+        <v>-1.13</v>
       </c>
       <c r="W15" t="n">
-        <v>2.2599</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>M. CAICEDO SANCHEZ</t>
+          <t>N. MC MULLEN</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.0974</v>
+        <v>-0.0864</v>
       </c>
       <c r="E16" t="n">
-        <v>1.9726</v>
+        <v>-0.6879</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.8752</v>
+        <v>0.6015</v>
       </c>
       <c r="G16" t="n">
-        <v>1.4499</v>
+        <v>-0.5832000000000001</v>
       </c>
       <c r="H16" t="n">
-        <v>0.7208</v>
+        <v>-0.666</v>
       </c>
       <c r="I16" t="n">
-        <v>0.7291</v>
+        <v>0.0829</v>
       </c>
       <c r="J16" t="n">
-        <v>2.3115</v>
+        <v>-0.7584</v>
       </c>
       <c r="K16" t="n">
-        <v>0.6086</v>
+        <v>-0.7966</v>
       </c>
       <c r="L16" t="n">
-        <v>1.7029</v>
+        <v>0.0382</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.8616</v>
+        <v>0.1752</v>
       </c>
       <c r="N16" t="n">
-        <v>0.1122</v>
+        <v>0.1306</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.9738</v>
+        <v>0.0446</v>
       </c>
       <c r="P16" t="n">
-        <v>0.435</v>
+        <v>-2.6101</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.0875</v>
+        <v>-3.2626</v>
       </c>
       <c r="R16" t="n">
-        <v>1.5225</v>
+        <v>0.6525</v>
       </c>
       <c r="S16" t="n">
-        <v>0.3425</v>
+        <v>0.8469</v>
       </c>
       <c r="T16" t="n">
-        <v>0.7487</v>
+        <v>1.0731</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.4062</v>
+        <v>-0.2262</v>
       </c>
       <c r="V16" t="n">
-        <v>-1.13</v>
+        <v>2.2599</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>2.2599</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.1871</v>
+        <v>-0.1062</v>
       </c>
       <c r="E17" t="n">
-        <v>0.7596000000000001</v>
+        <v>0.8714</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.9467</v>
+        <v>-0.9776</v>
       </c>
       <c r="G17" t="n">
         <v>-4.7506</v>
@@ -1780,13 +1780,13 @@
         <v>1.7401</v>
       </c>
       <c r="S17" t="n">
-        <v>0.5635</v>
+        <v>0.6444</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.1334</v>
+        <v>-0.0216</v>
       </c>
       <c r="U17" t="n">
-        <v>0.6969</v>
+        <v>0.666</v>
       </c>
       <c r="V17" t="n">
         <v>2.2599</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.0506</v>
+        <v>-1.1045</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.9194</v>
+        <v>-0.6959</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.1312</v>
+        <v>-0.4086</v>
       </c>
       <c r="G18" t="n">
         <v>0.9161</v>
@@ -1858,13 +1858,13 @@
         <v>0.87</v>
       </c>
       <c r="S18" t="n">
-        <v>0.3835</v>
+        <v>0.3296</v>
       </c>
       <c r="T18" t="n">
-        <v>0.1406</v>
+        <v>0.3641</v>
       </c>
       <c r="U18" t="n">
-        <v>0.2428</v>
+        <v>-0.0346</v>
       </c>
       <c r="V18" t="n">
         <v>1.13</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>M. STILMA</t>
+          <t>N. HOOVER</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.52</v>
+        <v>-2.0986</v>
       </c>
       <c r="E19" t="n">
-        <v>0.3818</v>
+        <v>-1.0729</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.9018</v>
+        <v>-1.0257</v>
       </c>
       <c r="G19" t="n">
-        <v>-2.9805</v>
+        <v>-0.264</v>
       </c>
       <c r="H19" t="n">
-        <v>-2.6825</v>
+        <v>1.7975</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.298</v>
+        <v>-2.0615</v>
       </c>
       <c r="J19" t="n">
-        <v>0.8613</v>
+        <v>1.3626</v>
       </c>
       <c r="K19" t="n">
-        <v>-1.4536</v>
+        <v>1.6853</v>
       </c>
       <c r="L19" t="n">
-        <v>2.3149</v>
+        <v>-0.3227</v>
       </c>
       <c r="M19" t="n">
-        <v>-3.8418</v>
+        <v>-1.6266</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.2289</v>
+        <v>0.1122</v>
       </c>
       <c r="O19" t="n">
-        <v>-2.6129</v>
+        <v>-1.7388</v>
       </c>
       <c r="P19" t="n">
-        <v>0.87</v>
+        <v>-1.0875</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-2.1751</v>
       </c>
       <c r="R19" t="n">
-        <v>0.87</v>
+        <v>1.0875</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.584</v>
+        <v>-0.1821</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.4795</v>
+        <v>0.1094</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.1046</v>
+        <v>-0.2914</v>
       </c>
       <c r="V19" t="n">
-        <v>0.1745</v>
+        <v>-0.5649999999999999</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>-0.3698</v>
       </c>
       <c r="X19" t="n">
-        <v>0.1745</v>
+        <v>-0.1952</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>N. HOOVER</t>
+          <t>M. STILMA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.0658</v>
+        <v>-2.1847</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.8552</v>
+        <v>0.7171</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.2106</v>
+        <v>-2.9018</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.264</v>
+        <v>-2.9805</v>
       </c>
       <c r="H20" t="n">
-        <v>1.7975</v>
+        <v>-2.6825</v>
       </c>
       <c r="I20" t="n">
-        <v>-2.0615</v>
+        <v>-0.298</v>
       </c>
       <c r="J20" t="n">
-        <v>1.3626</v>
+        <v>0.8613</v>
       </c>
       <c r="K20" t="n">
-        <v>1.6853</v>
+        <v>-1.4536</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.3227</v>
+        <v>2.3149</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.6266</v>
+        <v>-3.8418</v>
       </c>
       <c r="N20" t="n">
-        <v>0.1122</v>
+        <v>-1.2289</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.7388</v>
+        <v>-2.6129</v>
       </c>
       <c r="P20" t="n">
-        <v>-1.0875</v>
+        <v>0.87</v>
       </c>
       <c r="Q20" t="n">
-        <v>-2.1751</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.0875</v>
+        <v>0.87</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.1493</v>
+        <v>-0.2488</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.6729000000000001</v>
+        <v>-0.1442</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.4764</v>
+        <v>-0.1046</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.5649999999999999</v>
+        <v>0.1745</v>
       </c>
       <c r="W20" t="n">
-        <v>-0.3698</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.1952</v>
+        <v>0.1745</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.1337</v>
+        <v>-2.9833</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.5975</v>
+        <v>-1.2623</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.5361</v>
+        <v>-1.7211</v>
       </c>
       <c r="G21" t="n">
         <v>-3.3864</v>
@@ -2092,13 +2092,13 @@
         <v>0.87</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.4199</v>
+        <v>-1.2696</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.7534999999999999</v>
+        <v>-0.4182</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.6665</v>
+        <v>-0.8514</v>
       </c>
       <c r="V21" t="n">
         <v>1.8902</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.3971</v>
+        <v>-3.7632</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.0243</v>
+        <v>-1.3595</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.3728</v>
+        <v>-2.4036</v>
       </c>
       <c r="G22" t="n">
         <v>-3.4446</v>
@@ -2170,13 +2170,13 @@
         <v>1.5225</v>
       </c>
       <c r="S22" t="n">
-        <v>0.07199999999999999</v>
+        <v>-0.2941</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.1454</v>
+        <v>-0.4807</v>
       </c>
       <c r="U22" t="n">
-        <v>0.2174</v>
+        <v>0.1866</v>
       </c>
       <c r="V22" t="n">
         <v>1.7156</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.3954</v>
+        <v>-4.1103</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.8613</v>
+        <v>-1.6378</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.5341</v>
+        <v>-2.4725</v>
       </c>
       <c r="G23" t="n">
         <v>-3.8081</v>
@@ -2248,13 +2248,13 @@
         <v>1.7401</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.2399</v>
+        <v>-0.9547</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.0274</v>
+        <v>-0.8038999999999999</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.2125</v>
+        <v>-0.1508</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.594</v>
+        <v>-4.409</v>
       </c>
       <c r="E24" t="n">
         <v>-2.884</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.71</v>
+        <v>-1.525</v>
       </c>
       <c r="G24" t="n">
         <v>-3.7685</v>
@@ -2326,13 +2326,13 @@
         <v>1.0875</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.0207</v>
+        <v>-0.8358</v>
       </c>
       <c r="T24" t="n">
         <v>-0.8099</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.2108</v>
+        <v>-0.0258</v>
       </c>
       <c r="V24" t="n">
         <v>0.1952</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-8.171099999999999</v>
+        <v>-7.7626</v>
       </c>
       <c r="E25" t="n">
-        <v>-5.3226</v>
+        <v>-5.0991</v>
       </c>
       <c r="F25" t="n">
-        <v>-2.8485</v>
+        <v>-2.6635</v>
       </c>
       <c r="G25" t="n">
         <v>-5.7367</v>
@@ -2404,13 +2404,13 @@
         <v>1.0875</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.4317</v>
+        <v>-1.0232</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.9589</v>
+        <v>-0.7354000000000001</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.4728</v>
+        <v>-0.2878</v>
       </c>
       <c r="V25" t="n">
         <v>2.2599</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-27.8467</v>
+        <v>-27.84669999999999</v>
       </c>
       <c r="E26" t="n">
         <v>-11.4736</v>
       </c>
       <c r="F26" t="n">
-        <v>-16.373</v>
+        <v>-16.3731</v>
       </c>
       <c r="G26" t="n">
         <v>-26.3566</v>
@@ -2482,13 +2482,13 @@
         <v>13.0502</v>
       </c>
       <c r="S26" t="n">
-        <v>-2.98</v>
+        <v>-2.9802</v>
       </c>
       <c r="T26" t="n">
         <v>-1.4539</v>
       </c>
       <c r="U26" t="n">
-        <v>-1.5265</v>
+        <v>-1.5262</v>
       </c>
       <c r="V26" t="n">
         <v>10.1902</v>
